--- a/JsonConverter/JsonConverter/ExcelFiles/DropData.xlsx
+++ b/JsonConverter/JsonConverter/ExcelFiles/DropData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Oz6_07_RPG\Oz6-TeamPortfolio3D_RPG\JsonConverter\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43D9112-1B2A-406A-9A00-CD52EE71B28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF5E05C-FF42-4EC6-9079-67B9ECCC08B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="2190" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,12 +70,6 @@
     <t>MaxCount</t>
   </si>
   <si>
-    <t>drop_goblin_attack</t>
-  </si>
-  <si>
-    <t>mob_goblin_1</t>
-  </si>
-  <si>
     <t>Stat_02</t>
   </si>
   <si>
@@ -83,6 +77,14 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>mob_goblin_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropAttackDamage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -92,7 +94,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -133,6 +135,13 @@
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -215,7 +224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -247,6 +256,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -508,13 +520,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
@@ -538,14 +550,14 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>16</v>
       </c>
       <c r="D4" s="13">
         <v>0.2</v>

--- a/JsonConverter/JsonConverter/ExcelFiles/DropData.xlsx
+++ b/JsonConverter/JsonConverter/ExcelFiles/DropData.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Weapon" sheetId="1" r:id="R47390ec5efc44b60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Weapon" sheetId="1" r:id="R9f3134e501004ffe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -179,7 +179,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left"/>
@@ -216,6 +216,7 @@
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="1"/>
@@ -515,12 +516,24 @@
       <x:c r="O4" s="2"/>
     </x:row>
     <x:row r="5" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="4"/>
-      <x:c r="C5" s="4"/>
-      <x:c r="D5" s="2"/>
-      <x:c r="E5" s="2"/>
-      <x:c r="F5" s="2"/>
+      <x:c r="A5" s="3" t="str">
+        <x:v>dropAttackDamageSkeleton</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>mob_skeleton</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>Stat_02</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="G5" s="2"/>
       <x:c r="H5" s="2"/>
       <x:c r="I5" s="2"/>
@@ -532,12 +545,24 @@
       <x:c r="O5" s="2"/>
     </x:row>
     <x:row r="6" ht="15.75" customHeight="1">
-      <x:c r="A6" s="4"/>
-      <x:c r="B6" s="4"/>
-      <x:c r="C6" s="4"/>
-      <x:c r="D6" s="2"/>
-      <x:c r="E6" s="2"/>
-      <x:c r="F6" s="2"/>
+      <x:c r="A6" s="4" t="str">
+        <x:v>dropAttackDamageSkeletonV2</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="str">
+        <x:v>mob_skeletonv2</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="str">
+        <x:v>Stat_02</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="E6" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="G6" s="2"/>
       <x:c r="H6" s="2"/>
       <x:c r="I6" s="2"/>
@@ -549,12 +574,24 @@
       <x:c r="O6" s="2"/>
     </x:row>
     <x:row r="7" ht="15.75" customHeight="1">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="3"/>
-      <x:c r="C7" s="3"/>
-      <x:c r="D7" s="2"/>
-      <x:c r="E7" s="2"/>
-      <x:c r="F7" s="2"/>
+      <x:c r="A7" s="3" t="str">
+        <x:v>dropAttackDamageBoss</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>mob_Boss</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>Stat_02</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="G7" s="2"/>
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
